--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487037_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487037_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7961</v>
+        <v>7.6939</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9215</v>
+        <v>5.8997</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8746</v>
+        <v>1.7943</v>
       </c>
       <c r="G2" t="n">
         <v>5.3985</v>
@@ -610,13 +610,13 @@
         <v>2.8951</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0464</v>
+        <v>-1.1485</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0925</v>
+        <v>-0.1143</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9539</v>
+        <v>-1.0342</v>
       </c>
       <c r="V2" t="n">
         <v>1.5138</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.438</v>
+        <v>5.6294</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0206</v>
+        <v>6.1584</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5826</v>
+        <v>-0.529</v>
       </c>
       <c r="G3" t="n">
         <v>5.352</v>
@@ -688,13 +688,13 @@
         <v>2.8951</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5811</v>
+        <v>-1.3898</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.152</v>
+        <v>-0.0142</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4291</v>
+        <v>-1.3756</v>
       </c>
       <c r="V3" t="n">
         <v>-1.228</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1612</v>
+        <v>3.4388</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1477</v>
+        <v>3.586</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0135</v>
+        <v>-0.1471</v>
       </c>
       <c r="G4" t="n">
         <v>7.5416</v>
@@ -766,13 +766,13 @@
         <v>2.5091</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.56</v>
+        <v>-1.2823</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8196</v>
+        <v>-0.3814</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.901</v>
       </c>
       <c r="V4" t="n">
         <v>3.3558</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7498</v>
+        <v>3.0972</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0352</v>
+        <v>3.874</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2855</v>
+        <v>-0.7768</v>
       </c>
       <c r="G5" t="n">
         <v>4.191</v>
@@ -844,13 +844,13 @@
         <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.8971</v>
+        <v>-1.5497</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2492</v>
+        <v>-0.4104</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.6479</v>
+        <v>-1.1393</v>
       </c>
       <c r="V5" t="n">
         <v>1.228</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3453</v>
+        <v>0.5585</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2985</v>
+        <v>0.4582</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0468</v>
+        <v>0.1003</v>
       </c>
       <c r="G6" t="n">
         <v>0.4286</v>
@@ -922,13 +922,13 @@
         <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.6421</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3569</v>
+        <v>-0.1973</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4984</v>
+        <v>-0.4449</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6555</v>
+        <v>-2.3922</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0539</v>
+        <v>-0.2277</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7095</v>
+        <v>-2.1645</v>
       </c>
       <c r="G7" t="n">
         <v>1.9202</v>
@@ -1000,13 +1000,13 @@
         <v>1.7371</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2783</v>
+        <v>-0.4584</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4429</v>
+        <v>0.1613</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1646</v>
+        <v>-0.6197</v>
       </c>
       <c r="V7" t="n">
         <v>-4.626</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2299</v>
+        <v>-3.11</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8333</v>
+        <v>-2.8739</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3967</v>
+        <v>-0.2361</v>
       </c>
       <c r="G8" t="n">
         <v>-0.783</v>
@@ -1078,13 +1078,13 @@
         <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5169</v>
+        <v>-0.3969</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2512</v>
+        <v>0.2105</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7681</v>
+        <v>-0.6075</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8532</v>
+        <v>-3.9742</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0246</v>
+        <v>-1.0653</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8286</v>
+        <v>-2.9089</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3267</v>
@@ -1156,13 +1156,13 @@
         <v>0.579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2756</v>
+        <v>-0.3966</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2512</v>
+        <v>0.2105</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5268</v>
+        <v>-0.6071</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>9.751799999999999</v>
+        <v>10.9414</v>
       </c>
       <c r="E10" t="n">
-        <v>14.6195</v>
+        <v>15.8094</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.868</v>
+        <v>-4.8678</v>
       </c>
       <c r="G10" t="n">
         <v>22.7222</v>
@@ -1234,13 +1234,13 @@
         <v>14.4755</v>
       </c>
       <c r="S10" t="n">
-        <v>-8.4541</v>
+        <v>-7.2643</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7249</v>
+        <v>-0.5353000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.729200000000001</v>
+        <v>-6.7293</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6562999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.7658</v>
+        <v>4.4289</v>
       </c>
       <c r="E11" t="n">
-        <v>8.135</v>
+        <v>5.932</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3692</v>
+        <v>-1.5031</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5580000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>3.4741</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4359</v>
+        <v>2.099</v>
       </c>
       <c r="T11" t="n">
-        <v>3.9277</v>
+        <v>1.7246</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5083</v>
+        <v>0.3744</v>
       </c>
       <c r="V11" t="n">
         <v>0.5717</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2755</v>
+        <v>1.3381</v>
       </c>
       <c r="E12" t="n">
-        <v>3.13</v>
+        <v>3.0281</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8544</v>
+        <v>-1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3404</v>
+        <v>0.7819</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3411</v>
+        <v>-1.1717</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6815</v>
+        <v>1.9536</v>
       </c>
       <c r="J12" t="n">
-        <v>2.729</v>
+        <v>2.5172</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6233</v>
+        <v>0.0102</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1057</v>
+        <v>2.5069</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0694</v>
+        <v>-1.7353</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2822</v>
+        <v>-1.1819</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7872</v>
+        <v>-0.5534</v>
       </c>
       <c r="P12" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1231</v>
+        <v>0.386</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9368</v>
+        <v>0.1702</v>
       </c>
       <c r="T12" t="n">
-        <v>2.0451</v>
+        <v>0.511</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8915999999999999</v>
+        <v>-0.3407</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8166</v>
+        <v>0.0124</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3409</v>
+        <v>2.429</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5243</v>
+        <v>-2.4166</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.3646</v>
+        <v>-0.3404</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.336</v>
+        <v>1.3411</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.0285</v>
+        <v>-1.6815</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3873</v>
+        <v>2.729</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4194</v>
+        <v>2.6233</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0321</v>
+        <v>0.1057</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.9773</v>
+        <v>-3.0694</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9166</v>
+        <v>-1.2822</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.0607</v>
+        <v>-1.7872</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.0532</v>
+        <v>-1.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2811</v>
+        <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8833</v>
+        <v>1.6736</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7114</v>
+        <v>1.3442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1718</v>
+        <v>0.3295</v>
       </c>
       <c r="V13" t="n">
-        <v>3.0699</v>
+        <v>-1.5138</v>
       </c>
       <c r="W13" t="n">
-        <v>3.0699</v>
+        <v>0.2859</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>A. LOPEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.657</v>
+        <v>-0.1957</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4273</v>
+        <v>-0.0948</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7703</v>
+        <v>-0.101</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7819</v>
+        <v>-0.1806</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1717</v>
+        <v>-0.4233</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9536</v>
+        <v>0.2428</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5172</v>
+        <v>0.1997</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0102</v>
+        <v>0.0776</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5069</v>
+        <v>0.1221</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7353</v>
+        <v>-0.3802</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1819</v>
+        <v>-0.5009</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5534</v>
+        <v>0.1207</v>
       </c>
       <c r="P14" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>0.386</v>
+        <v>0.579</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5109</v>
+        <v>0.6567</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.08989999999999999</v>
+        <v>0.6706</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4211</v>
+        <v>-0.0139</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LOPEZ FERNANDEZ</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0573</v>
+        <v>-0.4317</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7958</v>
+        <v>0.0391</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2616</v>
+        <v>-0.4708</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1806</v>
+        <v>-4.3646</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4233</v>
+        <v>-2.336</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2428</v>
+        <v>-2.0285</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1997</v>
+        <v>-0.3873</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0776</v>
+        <v>-0.4194</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1221</v>
+        <v>0.0321</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3802</v>
+        <v>-3.9773</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5009</v>
+        <v>-1.9166</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1207</v>
+        <v>-2.0607</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.386</v>
+        <v>-0.772</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>-4.0532</v>
       </c>
       <c r="R15" t="n">
-        <v>0.579</v>
+        <v>3.2811</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2049</v>
+        <v>1.635</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0304</v>
+        <v>1.4096</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1745</v>
+        <v>0.2254</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2859</v>
+        <v>3.0699</v>
       </c>
       <c r="W15" t="n">
+        <v>3.0699</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.2859</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7407</v>
+        <v>-1.7813</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4914</v>
+        <v>-1.2911</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2493</v>
+        <v>-0.4903</v>
       </c>
       <c r="G16" t="n">
         <v>-2.1228</v>
@@ -1702,13 +1702,13 @@
         <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1818</v>
+        <v>0.1411</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4759</v>
+        <v>-0.2756</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6577</v>
+        <v>0.4167</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5717</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.1681</v>
+        <v>-2.5054</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3688</v>
+        <v>1.1333</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.7993</v>
+        <v>-3.6387</v>
       </c>
       <c r="G17" t="n">
         <v>-6.0648</v>
@@ -1780,13 +1780,13 @@
         <v>2.8951</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7403</v>
+        <v>0.9224</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5525</v>
+        <v>0.9496</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1877</v>
+        <v>-0.0271</v>
       </c>
       <c r="V17" t="n">
         <v>0.8999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.329</v>
+        <v>-4.5491</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5523</v>
+        <v>-2.8527</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7766</v>
+        <v>-1.6963</v>
       </c>
       <c r="G18" t="n">
         <v>-3.5497</v>
@@ -1858,13 +1858,13 @@
         <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7648</v>
+        <v>0.5447</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5619</v>
+        <v>0.2614</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2029</v>
+        <v>0.2832</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.9715</v>
+        <v>-6.0678</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.957</v>
+        <v>-3.4549</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0145</v>
+        <v>-2.6129</v>
       </c>
       <c r="G19" t="n">
         <v>-6.3235</v>
@@ -1936,13 +1936,13 @@
         <v>3.2811</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2922</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3682</v>
+        <v>0.1339</v>
       </c>
       <c r="U19" t="n">
-        <v>0.076</v>
+        <v>0.4775</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5138</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-9.7517</v>
+        <v>-9.7516</v>
       </c>
       <c r="E20" t="n">
-        <v>4.867900000000001</v>
+        <v>4.868</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.6195</v>
+        <v>-14.6197</v>
       </c>
       <c r="G20" t="n">
         <v>-22.7225</v>
@@ -2014,10 +2014,10 @@
         <v>18.3356</v>
       </c>
       <c r="S20" t="n">
-        <v>8.454300000000002</v>
+        <v>8.4541</v>
       </c>
       <c r="T20" t="n">
-        <v>6.729200000000001</v>
+        <v>6.729299999999999</v>
       </c>
       <c r="U20" t="n">
         <v>1.725</v>
